--- a/results-upload-template.xlsx
+++ b/results-upload-template.xlsx
@@ -607,13 +607,35 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>제43회 교육장기 육상경기대회</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>남자 100m</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2023.05.12</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>박민수</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>11.9초</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="n"/>
@@ -826,7 +848,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>작성 안내: '대회'는 반드시 '트랙마라톤 축제' 또는 '충북교육감기 육상대회' 중 하나를 정확히 입력(드롭다운 이용 권장). '순위'는 숫자만 입력(공동순위는 같은 숫자 사용 가능). '날짜','비고'는 선택 입력. 헤더 행(3행)은 수정하지 마세요.</t>
+          <t>작성 안내: '대회'는 반드시 '트랙마라톤 축제' / '충북교육감기 육상대회' / '제43회 교육장기 육상경기대회' 중 하나를 정확히 입력(드롭다운 이용 권장). '순위'는 숫자만 입력(공동순위는 같은 숫자 사용 가능). '날짜','비고'는 선택 입력. 헤더 행(3행)은 수정하지 마세요.</t>
         </is>
       </c>
     </row>
@@ -836,8 +858,8 @@
     <mergeCell ref="A35:F35"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="A4:A33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 대회명" error="정확한 대회명을 선택해 주세요 (트랙마라톤 축제 / 충북교육감기 육상대회)." type="list">
-      <formula1>"트랙마라톤 축제,충북교육감기 육상대회"</formula1>
+    <dataValidation sqref="A4:A33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 대회명" error="정확한 대회명을 선택해 주세요." type="list">
+      <formula1>"트랙마라톤 축제,충북교육감기 육상대회,제43회 교육장기 육상경기대회"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
